--- a/etc/hebrew/adverbs.xlsx
+++ b/etc/hebrew/adverbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -689,6 +689,48 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>at all; generally</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>בִּכְלָל</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>really; truly</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>בֶּאֱמֶת</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/adverbs.xlsx
+++ b/etc/hebrew/adverbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,27 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>less; minus</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>פָּחוֹת</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>adverb; math operator</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/adverbs.xlsx
+++ b/etc/hebrew/adverbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -752,6 +752,153 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>already</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>כְּבָר</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>more; still</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>עוֹד</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>tomorrow</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>מָחָר</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>תָּמִיד</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>approximately; about</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>בְּעֵרֶךְ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>בַּחוּץ</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>previously; before</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>קוֹדֶם</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/adverbs.xlsx
+++ b/etc/hebrew/adverbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -899,6 +899,48 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>especially; mainly</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>בְּעִיקָּר</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>immediately; right away</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>תֵּכֶף</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
